--- a/docs/BREATHE x-connects.xlsx
+++ b/docs/BREATHE x-connects.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/753886ee277e72f5/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jmacd\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4F4005C-F311-4472-81C8-D544C6D6A072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BAFE2DA-5235-4789-8B81-75DB2192EC81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2633" yWindow="712" windowWidth="12690" windowHeight="7733" xr2:uid="{7651A22A-F0EA-4E00-97EC-3F92CF68A73C}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{7651A22A-F0EA-4E00-97EC-3F92CF68A73C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="77">
   <si>
     <t>Breakout pin</t>
   </si>
@@ -259,6 +259,27 @@
   </si>
   <si>
     <t>interface to BME680, SCD41, VEML7700</t>
+  </si>
+  <si>
+    <t>ST7789 BLK</t>
+  </si>
+  <si>
+    <t>Si7021</t>
+  </si>
+  <si>
+    <t>VIN</t>
+  </si>
+  <si>
+    <t>SLC</t>
+  </si>
+  <si>
+    <t>SDA bus</t>
+  </si>
+  <si>
+    <t>SLA bus</t>
+  </si>
+  <si>
+    <t>XIAO D0</t>
   </si>
 </sst>
 </file>
@@ -361,10 +382,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -687,14 +704,14 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D50"/>
-  <sheetFormatPr defaultRowHeight="14.75" customHeight="1"/>
+  <dimension ref="A1:D55"/>
+  <sheetFormatPr defaultColWidth="9.04296875" defaultRowHeight="14.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="18.1328125" style="5" customWidth="1"/>
     <col min="2" max="2" width="12" style="6" customWidth="1"/>
-    <col min="3" max="3" width="36.73046875" style="6" customWidth="1"/>
+    <col min="3" max="3" width="36.7265625" style="6" customWidth="1"/>
     <col min="4" max="4" width="60" style="6" customWidth="1"/>
-    <col min="5" max="16384" width="9.06640625" style="6"/>
+    <col min="5" max="16384" width="9.04296875" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="5" customFormat="1" ht="14.75" customHeight="1">
@@ -758,7 +775,7 @@
         <v>34</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>36</v>
@@ -1111,8 +1128,8 @@
       <c r="B38" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C38" s="7" t="s">
-        <v>35</v>
+      <c r="C38" s="6" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="14.75" customHeight="1">
@@ -1236,6 +1253,50 @@
       </c>
       <c r="C50" s="7" t="s">
         <v>46</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="14.75" customHeight="1">
+      <c r="A52" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="14.75" customHeight="1">
+      <c r="A53" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="14.75" customHeight="1">
+      <c r="A54" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="14.75" customHeight="1">
+      <c r="A55" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
